--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484724_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484724_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7651</v>
+        <v>7.7211</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0148</v>
+        <v>3.2354</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7503</v>
+        <v>4.4857</v>
       </c>
       <c r="G2" t="n">
         <v>4.0478</v>
@@ -610,13 +610,13 @@
         <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5096</v>
+        <v>0.4656</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0669</v>
+        <v>0.2874</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4427</v>
+        <v>0.1782</v>
       </c>
       <c r="V2" t="n">
         <v>1.8868</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. AGBEKO</t>
+          <t>D. CAZORLA ZARAGOZI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9355</v>
+        <v>4.0027</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7929</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7284</v>
+        <v>4.5254</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.9245</v>
+        <v>1.0452</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.1804</v>
+        <v>-0.3467</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2558</v>
+        <v>1.3919</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.6912</v>
+        <v>-0.7019</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.7734</v>
+        <v>-0.6864</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0823</v>
+        <v>-0.0156</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2334</v>
+        <v>1.7471</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4069</v>
+        <v>0.3397</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1736</v>
+        <v>1.4075</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4531</v>
+        <v>2.2644</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0674</v>
+        <v>0.3914</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5401</v>
+        <v>-0.1225</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5273</v>
+        <v>0.5139</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2265</v>
+        <v>1.2452</v>
       </c>
       <c r="W3" t="n">
         <v>1.2452</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. CAZORLA ZARAGOZI</t>
+          <t>A. KLEINJAN RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7966</v>
+        <v>2.6066</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.5172</v>
+        <v>-1.2962</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3138</v>
+        <v>3.9028</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0452</v>
+        <v>2.8076</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3467</v>
+        <v>3.5264</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3919</v>
+        <v>-0.7188</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7019</v>
+        <v>1.8718</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6864</v>
+        <v>3.1538</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0156</v>
+        <v>-1.2821</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7471</v>
+        <v>0.9358</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3397</v>
+        <v>0.3725</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4075</v>
+        <v>0.5633</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3209</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2644</v>
+        <v>2.6418</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8147</v>
+        <v>-0.0123</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.117</v>
+        <v>-0.3375</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3022</v>
+        <v>0.3252</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. KLEINJAN RODRIGUEZ</t>
+          <t>R. AGBEKO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7683</v>
+        <v>1.878</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1345</v>
+        <v>-1.9033</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9028</v>
+        <v>3.7813</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8076</v>
+        <v>-1.9245</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5264</v>
+        <v>-2.1804</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7188</v>
+        <v>0.2558</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8718</v>
+        <v>-1.6912</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1538</v>
+        <v>-1.7734</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2821</v>
+        <v>0.0823</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9358</v>
+        <v>-0.2334</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3725</v>
+        <v>-0.4069</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5633</v>
+        <v>0.1736</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1887</v>
+        <v>0.5661</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6418</v>
+        <v>2.4531</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8506</v>
+        <v>1.0099</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1758</v>
+        <v>0.4296</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3252</v>
+        <v>0.5803</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.2265</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.9813</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>T. DESPLACE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5772</v>
+        <v>1.7461</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3238</v>
+        <v>-2.0721</v>
       </c>
       <c r="F6" t="n">
-        <v>1.901</v>
+        <v>3.8182</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8998</v>
+        <v>2.898</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4494</v>
+        <v>2.0167</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4504</v>
+        <v>0.8813</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5581</v>
+        <v>1.8652</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1254</v>
+        <v>1.807</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5673</v>
+        <v>0.0582</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3417</v>
+        <v>1.0329</v>
       </c>
       <c r="N6" t="n">
-        <v>0.324</v>
+        <v>0.2098</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0177</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1887</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1322</v>
+        <v>2.6418</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09229999999999999</v>
+        <v>-0.6425</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0617</v>
+        <v>-0.786</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0306</v>
+        <v>0.1435</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6036</v>
+        <v>-0.3208</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. DESPLACE</t>
+          <t>S. DAMULEVICIUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5298</v>
+        <v>1.728</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5795</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1092</v>
+        <v>1.1096</v>
       </c>
       <c r="G7" t="n">
-        <v>2.898</v>
+        <v>1.3954</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0167</v>
+        <v>0.7458</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8813</v>
+        <v>0.6496</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8652</v>
+        <v>0.6973</v>
       </c>
       <c r="K7" t="n">
-        <v>1.807</v>
+        <v>0.6973</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0582</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0329</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2098</v>
+        <v>0.0485</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.6496</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6418</v>
+        <v>0.7548</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8588</v>
+        <v>-0.4222</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2933</v>
+        <v>-0.0789</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4345</v>
+        <v>-0.3433</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. DAMULEVICIUS</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5247</v>
+        <v>1.0875</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5209</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0038</v>
+        <v>1.7422</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3954</v>
+        <v>1.8998</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7458</v>
+        <v>1.4494</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6496</v>
+        <v>0.4504</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6973</v>
+        <v>0.5581</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6973</v>
+        <v>1.1254</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.5673</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6981000000000001</v>
+        <v>1.3417</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0485</v>
+        <v>0.324</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6496</v>
+        <v>1.0177</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.3974</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1764</v>
+        <v>-0.2693</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4491</v>
+        <v>-0.1281</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.2107</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9019</v>
+        <v>-2.9406</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9661</v>
+        <v>3.1513</v>
       </c>
       <c r="G10" t="n">
         <v>0.3057</v>
@@ -1234,13 +1234,13 @@
         <v>2.0757</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4303</v>
+        <v>-0.2838</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2323</v>
+        <v>-0.2709</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1981</v>
+        <v>-0.0129</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9434</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. JIMENA LLORCA</t>
+          <t>M. MARZIALI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4627</v>
+        <v>-0.5311</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7731</v>
+        <v>-5.801</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3104</v>
+        <v>5.2699</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.1571</v>
+        <v>1.2293</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8343</v>
+        <v>0.5948</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3228</v>
+        <v>0.6345</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.5517</v>
+        <v>-0.3933</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0769</v>
+        <v>0.2066</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.4749</v>
+        <v>-0.5999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3946</v>
+        <v>1.6226</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2426</v>
+        <v>0.3882</v>
       </c>
       <c r="O11" t="n">
-        <v>0.152</v>
+        <v>1.2344</v>
       </c>
       <c r="P11" t="n">
-        <v>3.2079</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.7175</v>
       </c>
       <c r="R11" t="n">
         <v>3.2079</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1281</v>
+        <v>-0.2698</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4202</v>
+        <v>-0.6902</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2921</v>
+        <v>0.4204</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.019</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. MARZIALI</t>
+          <t>S. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1901</v>
+        <v>-0.5531</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.6981</v>
+        <v>-4.2603</v>
       </c>
       <c r="F12" t="n">
-        <v>5.508</v>
+        <v>3.7072</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2293</v>
+        <v>-3.1571</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5948</v>
+        <v>-0.8343</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6345</v>
+        <v>-2.3228</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3933</v>
+        <v>-3.5517</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2066</v>
+        <v>-1.0769</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5999</v>
+        <v>-2.4749</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6226</v>
+        <v>0.3946</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3882</v>
+        <v>0.2426</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2344</v>
+        <v>0.152</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5096</v>
+        <v>3.2079</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.7175</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>3.2079</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9288</v>
+        <v>0.0377</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5873</v>
+        <v>-0.067</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6585</v>
+        <v>0.1047</v>
       </c>
       <c r="V12" t="n">
-        <v>0.019</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.6256</v>
+        <v>20.2135</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.8683</v>
+        <v>-15.2801</v>
       </c>
       <c r="F13" t="n">
-        <v>35.4938</v>
+        <v>35.4936</v>
       </c>
       <c r="G13" t="n">
         <v>10.8642</v>
       </c>
       <c r="H13" t="n">
-        <v>8.373700000000001</v>
+        <v>8.373699999999999</v>
       </c>
       <c r="I13" t="n">
         <v>2.4904</v>
@@ -1459,7 +1459,7 @@
         <v>7.9051</v>
       </c>
       <c r="P13" t="n">
-        <v>6.604500000000001</v>
+        <v>6.6045</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.0395</v>
@@ -1468,16 +1468,16 @@
         <v>22.644</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7112999999999999</v>
+        <v>-0.1233999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.493199999999999</v>
+        <v>-1.9053</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7817</v>
+        <v>1.7819</v>
       </c>
       <c r="V13" t="n">
-        <v>2.868100000000001</v>
+        <v>2.8681</v>
       </c>
       <c r="W13" t="n">
         <v>2.131600000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9155</v>
+        <v>3.3754</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8592</v>
+        <v>1.372</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0563</v>
+        <v>2.0034</v>
       </c>
       <c r="G14" t="n">
         <v>1.9803</v>
@@ -1546,13 +1546,13 @@
         <v>1.5096</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6143</v>
+        <v>0.0742</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.2241</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.097</v>
+        <v>-0.1499</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6988</v>
+        <v>2.2192</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0516</v>
+        <v>-0.5073</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6471</v>
+        <v>2.7265</v>
       </c>
       <c r="G15" t="n">
         <v>1.677</v>
@@ -1624,13 +1624,13 @@
         <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8522</v>
+        <v>1.3726</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3072</v>
+        <v>0.7483</v>
       </c>
       <c r="U15" t="n">
-        <v>0.545</v>
+        <v>0.6243</v>
       </c>
       <c r="V15" t="n">
         <v>0.3018</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. GILABERT FERRI</t>
+          <t>J. GARCIA NAVEA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2041</v>
+        <v>0.0119</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7773</v>
+        <v>-2.6095</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5732</v>
+        <v>2.6214</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5854</v>
+        <v>1.8423</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1761</v>
+        <v>1.5198</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4093</v>
+        <v>0.3225</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1045</v>
+        <v>1.0434</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0634</v>
+        <v>1.717</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0411</v>
+        <v>-0.6737</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4809</v>
+        <v>0.799</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1127</v>
+        <v>-0.1972</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3682</v>
+        <v>0.9962</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.9435</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-3.0192</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.0757</v>
+      </c>
+      <c r="S16" t="n">
         <v>-0.5661</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.9435</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.3774</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-0.2234</v>
-      </c>
       <c r="T16" t="n">
-        <v>0.0617</v>
+        <v>-0.3128</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2851</v>
+        <v>-0.2533</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GARCIA NAVEA</t>
+          <t>C. CASTELLANOS MARTINEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3778</v>
+        <v>-0.2804</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.9992</v>
+        <v>-1.0058</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6214</v>
+        <v>0.7254</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8423</v>
+        <v>-1.0182</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5198</v>
+        <v>0.281</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3225</v>
+        <v>-1.2991</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0434</v>
+        <v>-1.278</v>
       </c>
       <c r="K17" t="n">
-        <v>1.717</v>
+        <v>0.0211</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6737</v>
+        <v>-1.2991</v>
       </c>
       <c r="M17" t="n">
-        <v>0.799</v>
+        <v>0.2598</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1972</v>
+        <v>0.2598</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9962</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0192</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0757</v>
+        <v>0.3774</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9558</v>
+        <v>0.3603</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7026</v>
+        <v>0.2722</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2533</v>
+        <v>0.0882</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. CASTELLANOS MARTINEZ</t>
+          <t>C. GILABERT FERRI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7231</v>
+        <v>-0.488</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3956</v>
+        <v>-1.167</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6725</v>
+        <v>0.679</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0182</v>
+        <v>0.5854</v>
       </c>
       <c r="H18" t="n">
-        <v>0.281</v>
+        <v>0.1761</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2991</v>
+        <v>0.4093</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.278</v>
+        <v>0.1045</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0211</v>
+        <v>0.0634</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2991</v>
+        <v>0.0411</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2598</v>
+        <v>0.4809</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2598</v>
+        <v>0.1127</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.3682</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3774</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R18" t="n">
         <v>0.3774</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0823</v>
+        <v>-0.5073</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1176</v>
+        <v>-0.3281</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0353</v>
+        <v>-0.1793</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0225</v>
+        <v>-0.9696</v>
       </c>
       <c r="E19" t="n">
         <v>-1.0611</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0386</v>
+        <v>0.0915</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2442</v>
@@ -1936,13 +1936,13 @@
         <v>0.3774</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2122</v>
+        <v>-0.1593</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0946</v>
+        <v>-0.0417</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.808</v>
+        <v>-0.9937</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8506</v>
+        <v>-3.1686</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0426</v>
+        <v>2.1749</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2439</v>
@@ -2014,13 +2014,13 @@
         <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3945</v>
+        <v>0.4199</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1634</v>
+        <v>-0.4814</v>
       </c>
       <c r="U20" t="n">
-        <v>0.769</v>
+        <v>0.9012</v>
       </c>
       <c r="V20" t="n">
         <v>0.6415999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3531</v>
+        <v>-2.362</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.642</v>
+        <v>-3.8625</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2889</v>
+        <v>1.5005</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8447</v>
@@ -2092,13 +2092,13 @@
         <v>1.5096</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6972</v>
+        <v>0.2939</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7055</v>
+        <v>0.074</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0083</v>
+        <v>0.2199</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2452</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8131</v>
+        <v>-3.4511</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.3541</v>
+        <v>-5.2567</v>
       </c>
       <c r="F22" t="n">
-        <v>1.541</v>
+        <v>1.8056</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2925</v>
@@ -2170,13 +2170,13 @@
         <v>2.4531</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.86</v>
+        <v>-0.4981</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5726</v>
+        <v>-0.4752</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2874</v>
+        <v>-0.0229</v>
       </c>
       <c r="V22" t="n">
         <v>-0.038</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6827</v>
+        <v>-5.1324</v>
       </c>
       <c r="E23" t="n">
         <v>-4.8871</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2044</v>
+        <v>-0.2453</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9687</v>
@@ -2248,13 +2248,13 @@
         <v>1.6983</v>
       </c>
       <c r="S23" t="n">
-        <v>0.418</v>
+        <v>-0.0318</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2199</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6379</v>
+        <v>0.1882</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8868</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. ANZULUNI</t>
+          <t>B. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8191</v>
+        <v>-5.7556</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.6245</v>
+        <v>-6.4233</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8054</v>
+        <v>0.6677</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4392</v>
+        <v>-4.8979</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.177</v>
+        <v>-3.5968</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7378</v>
+        <v>-1.3011</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4193</v>
+        <v>-4.7062</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4179</v>
+        <v>-2.7986</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0015</v>
+        <v>-1.9076</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8586</v>
+        <v>-0.1918</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5949</v>
+        <v>-0.7982</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7363</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-6.0384</v>
+        <v>0.1887</v>
       </c>
       <c r="Q24" t="n">
-        <v>-7.548</v>
+        <v>-0.9435</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5096</v>
+        <v>1.1322</v>
       </c>
       <c r="S24" t="n">
-        <v>1.9793</v>
+        <v>-1.0464</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0994</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>2.0788</v>
+        <v>-0.2727</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.9244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B. TERREROS RIVAS</t>
+          <t>M. ANZULUNI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.4364</v>
+        <v>-5.7992</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.8131</v>
+        <v>-6.9168</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3767</v>
+        <v>1.1176</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.8979</v>
+        <v>-0.4392</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.5968</v>
+        <v>-1.177</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.3011</v>
+        <v>0.7378</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.7062</v>
+        <v>0.4193</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.7986</v>
+        <v>0.4179</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.9076</v>
+        <v>0.0015</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1918</v>
+        <v>-0.8586</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7982</v>
+        <v>-1.5949</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.7363</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1887</v>
+        <v>-6.0384</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9435</v>
+        <v>-7.548</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7271</v>
+        <v>0.9992</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1634</v>
+        <v>-0.3917</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5637</v>
+        <v>1.3909</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-19.6256</v>
+        <v>-19.6255</v>
       </c>
       <c r="E26" t="n">
-        <v>-35.4938</v>
+        <v>-35.4937</v>
       </c>
       <c r="F26" t="n">
-        <v>15.8681</v>
+        <v>15.8682</v>
       </c>
       <c r="G26" t="n">
         <v>-10.8643</v>
@@ -2482,13 +2482,13 @@
         <v>16.0395</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7113</v>
+        <v>0.7111000000000002</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.7819</v>
+        <v>-1.7818</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4932</v>
+        <v>2.4929</v>
       </c>
       <c r="V26" t="n">
         <v>-2.8682</v>
